--- a/src/main/resources/FeatureFiles/CouchbaseVsMongoDbPage_Edge.xlsx
+++ b/src/main/resources/FeatureFiles/CouchbaseVsMongoDbPage_Edge.xlsx
@@ -186,9 +186,6 @@
     <t>Please check this box if you would like to be updated on offers, products and services from Couchbase. You can unsubscribe at any time. Please review our Privacy Policy for additional details.</t>
   </si>
   <si>
-    <t>openBrowser</t>
-  </si>
-  <si>
     <t>https://www.couchbase.com/comparing-couchbase-vs-mongodb-mobile/</t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>edge</t>
+  </si>
+  <si>
+    <t>openHeadlessBrowser</t>
   </si>
 </sst>
 </file>
@@ -684,10 +684,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>20</v>
@@ -698,7 +698,7 @@
         <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -706,7 +706,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,7 +714,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -730,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -741,7 +741,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -752,7 +752,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
@@ -763,7 +763,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
@@ -774,7 +774,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -785,7 +785,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
@@ -796,7 +796,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
@@ -807,7 +807,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -818,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -829,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -840,7 +840,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>12</v>
@@ -851,7 +851,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -859,7 +859,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -870,7 +870,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>25</v>
@@ -881,7 +881,7 @@
         <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>25</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>17</v>
@@ -903,7 +903,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>17</v>
@@ -914,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
@@ -925,7 +925,7 @@
         <v>38</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
@@ -936,7 +936,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
@@ -947,7 +947,7 @@
         <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>11</v>
@@ -958,7 +958,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -980,7 +980,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>12</v>
@@ -991,7 +991,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -999,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
@@ -1007,7 +1007,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>44</v>
@@ -1021,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>27</v>
@@ -1032,7 +1032,7 @@
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>28</v>
@@ -1043,7 +1043,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>6</v>
@@ -1054,7 +1054,7 @@
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>6</v>
@@ -1065,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
@@ -1076,7 +1076,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
@@ -1087,7 +1087,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
@@ -1098,7 +1098,7 @@
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>11</v>
@@ -1109,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
@@ -1120,7 +1120,7 @@
         <v>9</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>14</v>
@@ -1131,7 +1131,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>12</v>
@@ -1142,7 +1142,7 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1150,7 +1150,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1158,7 +1158,7 @@
         <v>26</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>29</v>
@@ -1172,7 +1172,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
@@ -1183,7 +1183,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>17</v>
@@ -1194,7 +1194,7 @@
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1205,7 @@
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>6</v>
@@ -1216,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>30</v>
@@ -1227,7 +1227,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>31</v>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>11</v>
@@ -1249,7 +1249,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>11</v>
@@ -1260,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -1271,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>14</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>12</v>
@@ -1293,7 +1293,7 @@
         <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -1301,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -1309,7 +1309,7 @@
         <v>26</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>29</v>
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>17</v>
@@ -1334,7 +1334,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>17</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>6</v>
@@ -1356,7 +1356,7 @@
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>6</v>
@@ -1367,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
         <v>32</v>
@@ -1378,7 +1378,7 @@
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>32</v>
@@ -1389,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>33</v>
@@ -1400,7 +1400,7 @@
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>33</v>
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>14</v>
@@ -1433,7 +1433,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>12</v>
@@ -1444,7 +1444,7 @@
         <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -1452,7 +1452,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -1460,7 +1460,7 @@
         <v>26</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>34</v>
@@ -1474,7 +1474,7 @@
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>17</v>
@@ -1485,7 +1485,7 @@
         <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>17</v>
@@ -1496,7 +1496,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>6</v>
@@ -1507,7 +1507,7 @@
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>6</v>
@@ -1518,7 +1518,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
         <v>32</v>
@@ -1529,7 +1529,7 @@
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>32</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>35</v>
@@ -1551,7 +1551,7 @@
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>35</v>
@@ -1562,7 +1562,7 @@
         <v>9</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>14</v>
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -1592,7 +1592,7 @@
         <v>4</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -1600,7 +1600,7 @@
         <v>26</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>36</v>
@@ -1614,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>17</v>
@@ -1625,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>17</v>
@@ -1636,7 +1636,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>6</v>
@@ -1647,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>6</v>
@@ -1658,7 +1658,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D100" t="s">
         <v>32</v>
@@ -1669,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>32</v>
@@ -1680,7 +1680,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>35</v>
@@ -1691,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>35</v>
@@ -1702,7 +1702,7 @@
         <v>9</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>10</v>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>12</v>
@@ -1724,7 +1724,7 @@
         <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
@@ -1732,7 +1732,7 @@
         <v>4</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -1740,7 +1740,7 @@
         <v>26</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>36</v>
@@ -1754,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>17</v>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>17</v>
@@ -1776,7 +1776,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>6</v>
@@ -1787,7 +1787,7 @@
         <v>16</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>6</v>
@@ -1798,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D114" t="s">
         <v>32</v>
@@ -1809,7 +1809,7 @@
         <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>32</v>
@@ -1820,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>35</v>
@@ -1831,7 +1831,7 @@
         <v>16</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>35</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>14</v>
@@ -1853,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>12</v>
@@ -1864,7 +1864,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
@@ -1872,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
@@ -1880,7 +1880,7 @@
         <v>26</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>36</v>
@@ -1888,13 +1888,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>6</v>
@@ -1905,7 +1905,7 @@
         <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>6</v>
@@ -1916,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>18</v>
@@ -1927,7 +1927,7 @@
         <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>18</v>
@@ -1938,7 +1938,7 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>11</v>
@@ -1949,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>11</v>
@@ -1960,7 +1960,7 @@
         <v>9</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>10</v>
@@ -1971,7 +1971,7 @@
         <v>9</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>14</v>
@@ -1982,7 +1982,7 @@
         <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>12</v>
@@ -1993,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
@@ -2001,7 +2001,7 @@
         <v>4</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
@@ -2009,7 +2009,7 @@
         <v>26</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>36</v>
@@ -2017,13 +2017,13 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>6</v>
@@ -2034,7 +2034,7 @@
         <v>16</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>6</v>
@@ -2045,7 +2045,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>17</v>
@@ -2056,7 +2056,7 @@
         <v>16</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>17</v>
@@ -2067,7 +2067,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>11</v>
@@ -2078,7 +2078,7 @@
         <v>16</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>11</v>
@@ -2089,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>10</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>14</v>
@@ -2111,7 +2111,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>12</v>
@@ -2122,7 +2122,7 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
@@ -2130,7 +2130,7 @@
         <v>4</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
@@ -2138,7 +2138,7 @@
         <v>26</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>36</v>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>6</v>
@@ -2163,7 +2163,7 @@
         <v>16</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>6</v>
@@ -2174,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>17</v>
@@ -2185,7 +2185,7 @@
         <v>16</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>17</v>
@@ -2196,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>18</v>
@@ -2207,7 +2207,7 @@
         <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>18</v>
@@ -2218,7 +2218,7 @@
         <v>5</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>11</v>
@@ -2229,7 +2229,7 @@
         <v>16</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>11</v>
@@ -2240,7 +2240,7 @@
         <v>9</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
@@ -2259,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="C161" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>17</v>
@@ -2270,7 +2270,7 @@
         <v>38</v>
       </c>
       <c r="C162" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>50</v>
@@ -2281,7 +2281,7 @@
         <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>51</v>
@@ -2292,7 +2292,7 @@
         <v>38</v>
       </c>
       <c r="C164" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>52</v>
@@ -2303,7 +2303,7 @@
         <v>9</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>14</v>
@@ -2314,7 +2314,7 @@
         <v>5</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>12</v>
@@ -2325,7 +2325,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
@@ -2333,18 +2333,18 @@
         <v>4</v>
       </c>
       <c r="C168" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>6</v>
@@ -2355,7 +2355,7 @@
         <v>16</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>6</v>
@@ -2366,7 +2366,7 @@
         <v>5</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>17</v>
@@ -2377,7 +2377,7 @@
         <v>16</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>17</v>
@@ -2388,7 +2388,7 @@
         <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>18</v>
@@ -2399,7 +2399,7 @@
         <v>16</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>18</v>
@@ -2410,7 +2410,7 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>11</v>
@@ -2421,7 +2421,7 @@
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>11</v>
@@ -2432,7 +2432,7 @@
         <v>9</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>49</v>
@@ -2443,7 +2443,7 @@
         <v>9</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>14</v>
@@ -2454,7 +2454,7 @@
         <v>5</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>12</v>
@@ -2465,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
@@ -2473,7 +2473,7 @@
         <v>4</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
@@ -2481,7 +2481,7 @@
         <v>26</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>36</v>
@@ -2489,13 +2489,13 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>6</v>
@@ -2506,7 +2506,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>6</v>
@@ -2517,7 +2517,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>17</v>
@@ -2528,7 +2528,7 @@
         <v>16</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>17</v>
@@ -2539,7 +2539,7 @@
         <v>5</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>18</v>
@@ -2550,7 +2550,7 @@
         <v>16</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>18</v>
@@ -2561,7 +2561,7 @@
         <v>5</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>11</v>
@@ -2572,7 +2572,7 @@
         <v>16</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>11</v>
@@ -2583,7 +2583,7 @@
         <v>9</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>53</v>
@@ -2594,7 +2594,7 @@
         <v>4</v>
       </c>
       <c r="C194" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.35">
@@ -2602,7 +2602,7 @@
         <v>9</v>
       </c>
       <c r="C195" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>54</v>
@@ -2613,7 +2613,7 @@
         <v>9</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>14</v>
@@ -2624,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>12</v>
@@ -2635,7 +2635,7 @@
         <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
@@ -2643,7 +2643,7 @@
         <v>13</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
@@ -2651,18 +2651,18 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>6</v>
@@ -2673,7 +2673,7 @@
         <v>16</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>6</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>17</v>
@@ -2695,7 +2695,7 @@
         <v>16</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>17</v>
@@ -2706,7 +2706,7 @@
         <v>5</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>18</v>
@@ -2717,7 +2717,7 @@
         <v>16</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>18</v>
@@ -2728,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>11</v>
@@ -2739,7 +2739,7 @@
         <v>16</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>11</v>
@@ -2750,7 +2750,7 @@
         <v>9</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>53</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>14</v>
@@ -2772,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>12</v>
@@ -2783,7 +2783,7 @@
         <v>13</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.35">
@@ -2791,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.35">
@@ -2799,7 +2799,7 @@
         <v>26</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>36</v>
@@ -2807,13 +2807,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>6</v>
@@ -2824,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>6</v>
@@ -2835,7 +2835,7 @@
         <v>5</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>17</v>
@@ -2846,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>17</v>
@@ -2857,7 +2857,7 @@
         <v>5</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>18</v>
@@ -2868,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>18</v>
@@ -2879,7 +2879,7 @@
         <v>5</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>11</v>
@@ -2890,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>11</v>
@@ -2901,7 +2901,7 @@
         <v>9</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>53</v>
@@ -2912,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="C226" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.35">
@@ -2920,7 +2920,7 @@
         <v>9</v>
       </c>
       <c r="C227" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>54</v>
@@ -2931,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>14</v>
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>12</v>
@@ -2953,7 +2953,7 @@
         <v>4</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
@@ -2961,7 +2961,7 @@
         <v>26</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>55</v>
@@ -2972,7 +2972,7 @@
         <v>13</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.35">
@@ -2980,7 +2980,7 @@
         <v>13</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
@@ -2988,7 +2988,7 @@
         <v>4</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.35">
